--- a/Result/profitability/3045.xlsx
+++ b/Result/profitability/3045.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM75"/>
+  <dimension ref="A1:AM76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>0.95</v>
       </c>
       <c r="M2" t="n">
-        <v>1.20125</v>
+        <v>1.215</v>
       </c>
       <c r="N2" t="n">
-        <v>25.03</v>
+        <v>25.18125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.20875</v>
+        <v>1.2525</v>
       </c>
       <c r="N3" t="n">
-        <v>29.38125</v>
+        <v>29.74</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -790,7 +790,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -897,10 +897,10 @@
         <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.23375</v>
+        <v>1.26875</v>
       </c>
       <c r="N4" t="n">
-        <v>33.83125</v>
+        <v>34.03625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1016,10 +1016,10 @@
         <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>1.25375</v>
+        <v>1.30375</v>
       </c>
       <c r="N5" t="n">
-        <v>37.99625</v>
+        <v>38.13125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1135,10 +1135,10 @@
         <v>1.06</v>
       </c>
       <c r="M6" t="n">
-        <v>1.25</v>
+        <v>1.2875</v>
       </c>
       <c r="N6" t="n">
-        <v>41.90875</v>
+        <v>42.015</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1262,10 +1262,10 @@
         <v>1.1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.23875</v>
+        <v>1.265</v>
       </c>
       <c r="N7" t="n">
-        <v>45.56</v>
+        <v>45.86625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1389,10 +1389,10 @@
         <v>1.21</v>
       </c>
       <c r="M8" t="n">
-        <v>1.23</v>
+        <v>1.245</v>
       </c>
       <c r="N8" t="n">
-        <v>49.51125</v>
+        <v>49.58625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         <v>1.20625</v>
       </c>
       <c r="N11" t="n">
-        <v>51.945</v>
+        <v>51.94500000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9951,6 +9951,133 @@
       </c>
       <c r="AM75" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>49432</v>
+      </c>
+      <c r="D76" t="n">
+        <v>38476</v>
+      </c>
+      <c r="E76" t="n">
+        <v>10956</v>
+      </c>
+      <c r="F76" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6119</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>12.38%</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>-70</v>
+      </c>
+      <c r="J76" t="n">
+        <v>6049</v>
+      </c>
+      <c r="K76" t="n">
+        <v>4539</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.26875</v>
+      </c>
+      <c r="N76" t="n">
+        <v>20.8225</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0.1199999999999999</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0.0875912408759123</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.02782931354359941</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.36697247706422</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1.080000000000002</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0.05123339658444026</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK76" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
